--- a/output/pdf_financials_xlsx/FFN.xlsx
+++ b/output/pdf_financials_xlsx/FFN.xlsx
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>57.596877</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>90.59423</v>
       </c>
     </row>
     <row r="35">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>57.596877</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>90.59423</v>
       </c>
     </row>
     <row r="37">
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>594.994188</v>
+        <v>537.3973109999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>810.836371</v>
+        <v>720.2421409999999</v>
       </c>
     </row>
     <row r="49">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" s="5" t="n">

--- a/output/pdf_financials_xlsx/FFN.xlsx
+++ b/output/pdf_financials_xlsx/FFN.xlsx
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3.265393</v>
+        <v>3.288976</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5.657186</v>
+        <v>5.679211</v>
       </c>
     </row>
     <row r="8">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>25.609659</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>13.742255</v>
       </c>
     </row>
     <row r="116">
@@ -2216,15 +2216,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>22.594782</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>57.596877</v>
       </c>
     </row>
     <row r="131">
@@ -2259,15 +2255,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>57.596877</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>90.59423</v>
       </c>
     </row>
     <row r="134">
@@ -3074,7 +3066,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
         <v>25.609659</v>
       </c>
@@ -3380,7 +3376,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>22.594782</v>
       </c>
@@ -3404,7 +3404,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>57.596877</v>
       </c>
@@ -5072,7 +5076,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E112" s="5" t="n">
         <v>0.023583</v>
       </c>
@@ -5348,7 +5356,11 @@
           <t>Distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E123" s="5" t="n">
         <v>-17.643603</v>
       </c>
